--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Recusa MDS 18-07-2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Recusa MDS 18-07-2025.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE00156-R0261486\ICM\Desktop\Recusa MDS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB3EC39-9B6C-49B3-B881-F876FBEC5269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15FEED0-7FD4-42F4-9BD9-17391355FD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{45EC382A-F1A6-4597-B2BA-20ECB6F33803}"/>
   </bookViews>
   <sheets>
-    <sheet name="MDS 17.07.2025" sheetId="1" r:id="rId1"/>
+    <sheet name="MDS 18.07.2025" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -62,13 +62,16 @@
     <t>Allianz</t>
   </si>
   <si>
-    <t xml:space="preserve">ALBRECHT CARSTEN WEGENER                     </t>
+    <t xml:space="preserve">AILA MOTA DA SILVA                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICK PISANI BAUDON                        </t>
   </si>
   <si>
     <t>Desistência</t>
   </si>
   <si>
-    <t>Recusa a pedido do corretor</t>
+    <t>Recusa a pedido corretor</t>
   </si>
 </sst>
 </file>
@@ -468,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161CC06E-3A90-4832-A482-7E1143079858}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -508,30 +511,53 @@
         <v>7</v>
       </c>
       <c r="B2" s="3">
-        <v>45855</v>
+        <v>45857</v>
       </c>
       <c r="C2" s="3">
-        <v>45855</v>
+        <v>45856</v>
       </c>
       <c r="D2" s="4">
-        <v>133483753</v>
+        <v>133464716</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>45855</v>
+      </c>
+      <c r="C3" s="3">
+        <v>45856</v>
+      </c>
+      <c r="D3" s="4">
+        <v>133489026</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F3" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{AD04ACF8-212D-4C98-AFC8-6022B8EC252B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3" xr:uid="{AD04ACF8-212D-4C98-AFC8-6022B8EC252B}">
       <formula1>"Bônus,Falta de Vistoria,Falta de Inspeção,Demais Motivos,CAP,Vistoria Recusada,Fora da Politica,Desistência,Falta Laudo Cautelar,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{141A97CD-FF49-4E7F-B1F9-0136CA0F30C3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A3" xr:uid="{141A97CD-FF49-4E7F-B1F9-0136CA0F30C3}">
       <formula1>"Allianz,"</formula1>
     </dataValidation>
   </dataValidations>
